--- a/src/Excelsior.Tests/DictionarySheetTests.FormulaWithStringRef.verified.xlsx
+++ b/src/Excelsior.Tests/DictionarySheetTests.FormulaWithStringRef.verified.xlsx
@@ -60,7 +60,7 @@
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="9" style="4" customWidth="1"/>
+    <col min="4" max="4" width="12" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
